--- a/Assets/Datas/MortalGames.xlsx
+++ b/Assets/Datas/MortalGames.xlsx
@@ -1715,7 +1715,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -1789,7 +1789,79 @@
         <v>168</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>CardSelection_Default</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>選擇卡片</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>CardSelection_Step</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>步驟 {0}/{1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>CardSelection_Optional</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>已選 {0}/{1} 張，最多選 {1} 張</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>CardSelection_Required</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>已選 {0}/{1} 張，必須選滿</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>CardSelection_Rejected</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>這次出牌無法完成，請關閉後重新操作。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>CardSelection_InsufficientCandidates</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>可選卡片不足，無法完成這次出牌。請關閉後重新操作。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <drawing ns1:id="rId1"/>
 </worksheet>
 </file>